--- a/cs2_mouse_tracking.xlsx
+++ b/cs2_mouse_tracking.xlsx
@@ -474,25 +474,17 @@
           <t>Pulsar ZywOo The Chosen Mouse Gen.2</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>800.00</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>800</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,25 +513,17 @@
           <t>Razer DeathAdder V3 HyperSpeed</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>400</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="F3" t="n">
+        <v>708</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -568,25 +552,17 @@
           <t>ZOWIE EC2-DW Grey (Unreleased)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1200.00</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>400</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -615,25 +591,17 @@
           <t>ZOWIE EC2-DW Black</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>764.00</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>400</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F5" t="n">
+        <v>764</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -662,25 +630,17 @@
           <t>VAXEE XE V2 Fluorescent Green</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>760.00</t>
-        </is>
+      <c r="C6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>400</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>760</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -709,25 +669,17 @@
           <t>ZOWIE x donk Mouse (Unreleased)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>800</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -756,25 +708,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>832.00</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>800</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F8" t="n">
+        <v>832</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -803,25 +747,17 @@
           <t>Endgame Gear OP1 8k V2 Black</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>600.00</t>
-        </is>
+      <c r="C9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D9" t="n">
+        <v>400</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>600</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -850,25 +786,17 @@
           <t>Logitech G Pro X Superlight 2 Magenta</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>840.00</t>
-        </is>
+      <c r="C10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>800</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>840</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -897,25 +825,17 @@
           <t>VAXEE ZYGEN NP-01S V2 Wireless Pink</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>560.00</t>
-        </is>
+      <c r="C11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>400</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>560</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -944,25 +864,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>400.00</t>
-        </is>
+      <c r="C12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>800</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>400</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -991,25 +903,17 @@
           <t>Logitech G Pro X Superlight 2 Black</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>600.00</t>
-        </is>
+      <c r="C13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D13" t="n">
+        <v>400</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>600</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1038,25 +942,17 @@
           <t>Razer Deathadder V3 Pro White</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>990.00</t>
-        </is>
+      <c r="C14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>900</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>990</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1085,25 +981,17 @@
           <t>ZOWIE EC2-CW</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>920.00</t>
-        </is>
+      <c r="C15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>800</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F15" t="n">
+        <v>920</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1132,25 +1020,17 @@
           <t>ZOWIE EC1-C</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>880</t>
-        </is>
+      <c r="C16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>400</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>880</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1179,25 +1059,17 @@
           <t>Razer DeathAdder V3 HyperSpeed</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="C17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>800</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>800</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1226,25 +1098,17 @@
           <t>Logitech G Pro X Superlight 2 Black</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>600.00</t>
-        </is>
+      <c r="C18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D18" t="n">
+        <v>400</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>600</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1273,25 +1137,17 @@
           <t>Logitech G Pro X Superlight 2 White</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
+      <c r="C19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>400</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>920</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1320,25 +1176,17 @@
           <t>Razer DeathAdder V4 Pro NiKo Edition</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>720.00</t>
-        </is>
+      <c r="C20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>800</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>720</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1367,25 +1215,17 @@
           <t>Razer DeathAdder V3 HyperSpeed</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>720.00</t>
-        </is>
+      <c r="C21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>800</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>720</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1414,25 +1254,17 @@
           <t>Razer Viper V4 Pro White</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>880.00</t>
-        </is>
+      <c r="C22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F22" t="n">
+        <v>880</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1461,25 +1293,17 @@
           <t>Razer DeathAdder V4 Pro Green</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1120.00</t>
-        </is>
+      <c r="C23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D23" t="n">
+        <v>800</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1120</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1508,25 +1332,17 @@
           <t>Logitech G Pro X Superlight 2 Black</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1024.00</t>
-        </is>
+      <c r="C24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D24" t="n">
+        <v>800</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1024</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1555,25 +1371,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>580.00</t>
-        </is>
+      <c r="C25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D25" t="n">
+        <v>400</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F25" t="n">
+        <v>580</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1602,25 +1410,17 @@
           <t>ZOWIE EC2-DW Black</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>920.00</t>
-        </is>
+      <c r="C26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D26" t="n">
+        <v>400</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>920</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1649,25 +1449,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>1000.00</t>
-        </is>
+      <c r="C27" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D27" t="n">
+        <v>400</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1000</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1696,25 +1488,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
+      <c r="C28" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D28" t="n">
+        <v>400</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1200</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1743,25 +1527,17 @@
           <t>Logitech G Pro X Superlight 2 White</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>800.00</t>
-        </is>
+      <c r="C29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D29" t="n">
+        <v>800</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>800</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1790,25 +1566,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1120.00</t>
-        </is>
+      <c r="C30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D30" t="n">
+        <v>800</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1120</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1837,25 +1605,17 @@
           <t>ZOWIE FK1-C</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
+      <c r="C31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D31" t="n">
+        <v>400</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>920</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1884,25 +1644,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>1600.00</t>
-        </is>
+      <c r="C32" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1600</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1931,25 +1683,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1440.00</t>
-        </is>
+      <c r="C33" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D33" t="n">
+        <v>800</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1440</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1978,25 +1722,17 @@
           <t>Logitech G Pro X Superlight Red</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>1160.00</t>
-        </is>
+      <c r="C34" t="n">
+        <v>500</v>
+      </c>
+      <c r="D34" t="n">
+        <v>800</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1160</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2025,25 +1761,17 @@
           <t>Zowie ZA12-DW</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1120.00</t>
-        </is>
+      <c r="C35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D35" t="n">
+        <v>800</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1120</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2072,25 +1800,17 @@
           <t>Logitech G Pro X Superlight 2 Cyan</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.825</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>660.00</t>
-        </is>
+      <c r="C36" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D36" t="n">
+        <v>800</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="F36" t="n">
+        <v>660</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2119,25 +1839,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="C37" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D37" t="n">
+        <v>800</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>800</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2166,25 +1878,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>1016.00</t>
-        </is>
+      <c r="C38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D38" t="n">
+        <v>800</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1016</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2213,25 +1917,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
+      <c r="C39" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D39" t="n">
+        <v>400</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>920</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2260,25 +1956,17 @@
           <t>Logitech G Pro X Superlight Red</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>848.00</t>
-        </is>
+      <c r="C40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D40" t="n">
+        <v>800</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="F40" t="n">
+        <v>848</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2307,25 +1995,17 @@
           <t>Logitech G Pro X Superlight 2 Magenta</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1040.00</t>
-        </is>
+      <c r="C41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D41" t="n">
+        <v>800</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1040</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2354,25 +2034,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1000.00</t>
-        </is>
+      <c r="C42" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D42" t="n">
+        <v>800</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2401,25 +2073,17 @@
           <t>ZOWIE EC2-DW Black</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>920.00</t>
-        </is>
+      <c r="C43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D43" t="n">
+        <v>400</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>920</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2448,25 +2112,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>720.00</t>
-        </is>
+      <c r="C44" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D44" t="n">
+        <v>400</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F44" t="n">
+        <v>720</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2495,25 +2151,17 @@
           <t>Logitech G Pro X Superlight Magenta</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
+      <c r="C45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D45" t="n">
+        <v>400</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1240</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2542,25 +2190,17 @@
           <t>Razer Viper V4 Pro White</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>656.00</t>
-        </is>
+      <c r="C46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D46" t="n">
+        <v>800</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F46" t="n">
+        <v>656</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2589,25 +2229,17 @@
           <t>Logitech G Pro X Superlight 2 Black</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>1108.00</t>
-        </is>
+      <c r="C47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D47" t="n">
+        <v>400</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1108</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2636,25 +2268,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>1040.00</t>
-        </is>
+      <c r="C48" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1040</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2683,25 +2307,17 @@
           <t>ZOWIE EC2-DW Black</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>680.00</t>
-        </is>
+      <c r="C49" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D49" t="n">
+        <v>400</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F49" t="n">
+        <v>680</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2730,25 +2346,17 @@
           <t>Logitech G Pro X Superlight 2 White</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>640.00</t>
-        </is>
+      <c r="C50" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D50" t="n">
+        <v>800</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F50" t="n">
+        <v>640</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2777,25 +2385,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>760.00</t>
-        </is>
+      <c r="C51" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D51" t="n">
+        <v>800</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F51" t="n">
+        <v>760</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2824,25 +2424,17 @@
           <t>Razer Viper V4 Pro White</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="C52" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D52" t="n">
+        <v>400</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>800</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2871,25 +2463,17 @@
           <t>Razer Viper V4 Pro White</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
+      <c r="C53" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D53" t="n">
+        <v>400</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F53" t="n">
+        <v>680</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2918,25 +2502,17 @@
           <t>Razer DeathAdder V4 Pro Black</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="C54" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D54" t="n">
+        <v>400</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" t="n">
+        <v>800</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2965,25 +2541,17 @@
           <t>WLMouse x DRG Beast X Max Green</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>760.00</t>
-        </is>
+      <c r="C55" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D55" t="n">
+        <v>400</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F55" t="n">
+        <v>760</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3012,25 +2580,17 @@
           <t>Logitech G Pro X Superlight 2 Black</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>1000.00</t>
-        </is>
+      <c r="C56" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D56" t="n">
+        <v>800</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1000</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3059,25 +2619,17 @@
           <t>Logitech G Pro X Superlight 2 Magenta</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="C57" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D57" t="n">
+        <v>400</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" t="n">
+        <v>800</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3106,25 +2658,17 @@
           <t>Razer DeathAdder V4 Pro Black</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>920.00</t>
-        </is>
+      <c r="C58" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D58" t="n">
+        <v>800</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F58" t="n">
+        <v>920</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3153,25 +2697,17 @@
           <t>Dareu A950 Pro</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1000.00</t>
-        </is>
+      <c r="C59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D59" t="n">
+        <v>800</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1000</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3200,25 +2736,17 @@
           <t>Logitech G Pro X Superlight 2 Magenta</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
+      <c r="C60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D60" t="n">
+        <v>800</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F60" t="n">
+        <v>720</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3247,25 +2775,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>984.00</t>
-        </is>
+      <c r="C61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D61" t="n">
+        <v>800</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F61" t="n">
+        <v>984</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3294,25 +2814,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>656.00</t>
-        </is>
+      <c r="C62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F62" t="n">
+        <v>656</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3341,25 +2853,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>560.00</t>
-        </is>
+      <c r="C63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D63" t="n">
+        <v>800</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F63" t="n">
+        <v>560</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3388,25 +2892,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>816.00</t>
-        </is>
+      <c r="C64" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D64" t="n">
+        <v>800</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="F64" t="n">
+        <v>816</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3435,25 +2931,17 @@
           <t>Logitech G Pro X Superlight 2 Magenta</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>720.00</t>
-        </is>
+      <c r="C65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D65" t="n">
+        <v>600</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F65" t="n">
+        <v>720</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3482,25 +2970,17 @@
           <t>Razer Viper V4 Pro Black</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>720.00</t>
-        </is>
+      <c r="C66" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D66" t="n">
+        <v>800</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F66" t="n">
+        <v>720</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3529,25 +3009,17 @@
           <t>ZOWIE EC2-DW Glossy</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
+      <c r="C67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D67" t="n">
+        <v>800</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F67" t="n">
+        <v>720</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3576,25 +3048,17 @@
           <t>Logitech G Pro X Superlight 2 Black</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>800.00</t>
-        </is>
+      <c r="C68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D68" t="n">
+        <v>800</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>800</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3623,25 +3087,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1000.00</t>
-        </is>
+      <c r="C69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D69" t="n">
+        <v>800</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1000</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3670,25 +3126,17 @@
           <t>Razer Deathadder V3 Pro White</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="C70" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D70" t="n">
+        <v>400</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" t="n">
+        <v>800</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3717,25 +3165,17 @@
           <t>Fallen Gear Lobo Wireless</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>800.00</t>
-        </is>
+      <c r="C71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D71" t="n">
+        <v>400</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" t="n">
+        <v>800</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3764,25 +3204,17 @@
           <t>ZOWIE EC2-DW Black</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>960.00</t>
-        </is>
+      <c r="C72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D72" t="n">
+        <v>800</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F72" t="n">
+        <v>960</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3811,25 +3243,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>1160.00</t>
-        </is>
+      <c r="C73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D73" t="n">
+        <v>800</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1160</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3858,25 +3282,17 @@
           <t>Razer Viper V4 Pro Black</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>1000.00</t>
-        </is>
+      <c r="C74" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D74" t="n">
+        <v>800</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1000</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3905,25 +3321,17 @@
           <t>ZOWIE EC2-DW Black</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>760.00</t>
-        </is>
+      <c r="C75" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D75" t="n">
+        <v>400</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F75" t="n">
+        <v>760</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3952,25 +3360,17 @@
           <t>Razer Deathadder V3 Pro White</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>568.00</t>
-        </is>
+      <c r="C76" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D76" t="n">
+        <v>400</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F76" t="n">
+        <v>568</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3999,25 +3399,17 @@
           <t>Pulsar eS FS-1</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>1080.00</t>
-        </is>
+      <c r="C77" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D77" t="n">
+        <v>400</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1080</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4046,25 +3438,17 @@
           <t>HITSCAN Hyperlight White</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>1.323</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>1058.40</t>
-        </is>
+      <c r="C78" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D78" t="n">
+        <v>800</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1058.4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -4093,25 +3477,17 @@
           <t>ZOWIE U2-DW Black</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>800.00</t>
-        </is>
+      <c r="C79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D79" t="n">
+        <v>800</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>800</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4140,25 +3516,17 @@
           <t>Logitech G Pro X Superlight 2 Black</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="C80" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D80" t="n">
+        <v>400</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2</v>
+      </c>
+      <c r="F80" t="n">
+        <v>800</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4187,25 +3555,17 @@
           <t>Logitech G Pro X Superlight 2 Magenta</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="C81" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D81" t="n">
+        <v>400</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" t="n">
+        <v>800</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4234,25 +3594,17 @@
           <t>Razer DeathAdder V4 Pro Green</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>1088.00</t>
-        </is>
+      <c r="C82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D82" t="n">
+        <v>800</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1088</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4281,25 +3633,17 @@
           <t>ZOWIE U2-DW Grey (Unreleased)</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>760.00</t>
-        </is>
+      <c r="C83" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D83" t="n">
+        <v>800</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F83" t="n">
+        <v>760</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4328,25 +3672,17 @@
           <t>VAXEE NP-01S V3 Pink</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>880.00</t>
-        </is>
+      <c r="C84" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D84" t="n">
+        <v>800</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>880</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4375,25 +3711,17 @@
           <t>ZOWIE EC2-DW Black</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>716.00</t>
-        </is>
+      <c r="C85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D85" t="n">
+        <v>400</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F85" t="n">
+        <v>716</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4422,25 +3750,17 @@
           <t>ZOWIE S2-DW Black</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>1000.00</t>
-        </is>
+      <c r="C86" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D86" t="n">
+        <v>800</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1000</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4469,25 +3789,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>960.00</t>
-        </is>
+      <c r="C87" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D87" t="n">
+        <v>800</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F87" t="n">
+        <v>960</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4516,25 +3828,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1040.00</t>
-        </is>
+      <c r="C88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D88" t="n">
+        <v>800</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1040</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4563,25 +3867,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>720.00</t>
-        </is>
+      <c r="C89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D89" t="n">
+        <v>400</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F89" t="n">
+        <v>720</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4610,25 +3906,17 @@
           <t>Logitech G Pro X Superlight 2 White</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>800.00</t>
-        </is>
+      <c r="C90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D90" t="n">
+        <v>800</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>800</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4657,25 +3945,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>520.00</t>
-        </is>
+      <c r="C91" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D91" t="n">
+        <v>800</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F91" t="n">
+        <v>520</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4704,25 +3984,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+      <c r="C92" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D92" t="n">
+        <v>800</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1000</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4751,25 +4023,17 @@
           <t>ZOWIE EC2-CW</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>1000.00</t>
-        </is>
+      <c r="C93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D93" t="n">
+        <v>400</v>
+      </c>
+      <c r="E93" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1000</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4798,25 +4062,17 @@
           <t>ZOWIE EC2-DW Black</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>888.00</t>
-        </is>
+      <c r="C94" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D94" t="n">
+        <v>800</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F94" t="n">
+        <v>888</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4845,25 +4101,17 @@
           <t>ZOWIE EC2-DW Glossy</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>800.00</t>
-        </is>
+      <c r="C95" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D95" t="n">
+        <v>800</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>800</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4892,25 +4140,17 @@
           <t>ZOWIE ZA13-DW Black</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>660.00</t>
-        </is>
+      <c r="C96" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D96" t="n">
+        <v>400</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F96" t="n">
+        <v>660</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4939,25 +4179,17 @@
           <t>Lamzu Maya X Purple Shadow</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>732</t>
-        </is>
+      <c r="C97" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D97" t="n">
+        <v>400</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F97" t="n">
+        <v>732</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4986,25 +4218,17 @@
           <t>Logitech G Pro X Superlight 2 Black</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
+      <c r="C98" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D98" t="n">
+        <v>400</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F98" t="n">
+        <v>660</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -5033,25 +4257,17 @@
           <t>ZOWIE EC1-DW Black</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>768.00</t>
-        </is>
+      <c r="C99" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D99" t="n">
+        <v>400</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F99" t="n">
+        <v>768</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5080,25 +4296,17 @@
           <t>ZOWIE EC2-DW Glossy</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="C100" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D100" t="n">
+        <v>400</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" t="n">
+        <v>800</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5127,25 +4335,17 @@
           <t>ZOWIE EC2-DW Black</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>800.00</t>
-        </is>
+      <c r="C101" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D101" t="n">
+        <v>800</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" t="n">
+        <v>800</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5174,25 +4374,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>1160.00</t>
-        </is>
+      <c r="C102" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D102" t="n">
+        <v>800</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1160</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5221,25 +4413,17 @@
           <t>ZOWIE U2-DW Black</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
+      <c r="C103" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D103" t="n">
+        <v>400</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="F103" t="n">
+        <v>708</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5268,25 +4452,17 @@
           <t>ZOWIE EC2-DW Black</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>1236.00</t>
-        </is>
+      <c r="C104" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D104" t="n">
+        <v>400</v>
+      </c>
+      <c r="E104" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1236</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5315,25 +4491,17 @@
           <t>ZOWIE EC1-DW Grey (Unreleased)</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>700.00</t>
-        </is>
+      <c r="C105" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D105" t="n">
+        <v>400</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F105" t="n">
+        <v>700</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5362,25 +4530,17 @@
           <t>ZOWIE EC2-DW Black</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
+      <c r="C106" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D106" t="n">
+        <v>400</v>
+      </c>
+      <c r="E106" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1224</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5409,25 +4569,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
+      <c r="C107" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D107" t="n">
+        <v>800</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F107" t="n">
+        <v>960</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5456,25 +4608,17 @@
           <t>Razer Viper V3 Pro White</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>800.00</t>
-        </is>
+      <c r="C108" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D108" t="n">
+        <v>800</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" t="n">
+        <v>800</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -5503,25 +4647,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>640.00</t>
-        </is>
+      <c r="C109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D109" t="n">
+        <v>800</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F109" t="n">
+        <v>640</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -5550,25 +4686,17 @@
           <t>VAXEE XE V2 Black</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
+      <c r="C110" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D110" t="n">
+        <v>800</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1600</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -5597,25 +4725,17 @@
           <t>Razer Viper V3 Pro Green</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>800.00</t>
-        </is>
+      <c r="C111" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D111" t="n">
+        <v>800</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" t="n">
+        <v>800</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -5644,25 +4764,17 @@
           <t>VAXEE XE V2 Lake Green</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>880</t>
-        </is>
+      <c r="C112" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D112" t="n">
+        <v>400</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F112" t="n">
+        <v>880</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -5691,25 +4803,17 @@
           <t>ZOWIE S2-DW Grey (Unreleased)</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>848</t>
-        </is>
+      <c r="C113" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D113" t="n">
+        <v>400</v>
+      </c>
+      <c r="E113" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F113" t="n">
+        <v>848</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -5738,25 +4842,17 @@
           <t>ZOWIE S2-DW Glossy</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>1016.00</t>
-        </is>
+      <c r="C114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D114" t="n">
+        <v>800</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1016</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -5785,25 +4881,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="C115" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D115" t="n">
+        <v>400</v>
+      </c>
+      <c r="E115" t="n">
+        <v>2</v>
+      </c>
+      <c r="F115" t="n">
+        <v>800</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -5832,25 +4920,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>1200.00</t>
-        </is>
+      <c r="C116" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D116" t="n">
+        <v>400</v>
+      </c>
+      <c r="E116" t="n">
+        <v>3</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1200</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -5879,25 +4959,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>708.00</t>
-        </is>
+      <c r="C117" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D117" t="n">
+        <v>400</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="F117" t="n">
+        <v>708</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -5926,25 +4998,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>920.00</t>
-        </is>
+      <c r="C118" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D118" t="n">
+        <v>400</v>
+      </c>
+      <c r="E118" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F118" t="n">
+        <v>920</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -5973,25 +5037,17 @@
           <t>ZOWIE FK2-DW Black</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>1000.00</t>
-        </is>
+      <c r="C119" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D119" t="n">
+        <v>800</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1000</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -6020,25 +5076,17 @@
           <t>ZOWIE EC2-DW Grey (Unreleased)</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>640.00</t>
-        </is>
+      <c r="C120" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D120" t="n">
+        <v>800</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F120" t="n">
+        <v>640</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6067,25 +5115,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>640.00</t>
-        </is>
+      <c r="C121" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D121" t="n">
+        <v>800</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F121" t="n">
+        <v>640</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -6114,25 +5154,17 @@
           <t>Pulsar X2H CrazyLight Medium</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>1000.00</t>
-        </is>
+      <c r="C122" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D122" t="n">
+        <v>800</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1000</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -6161,25 +5193,17 @@
           <t>Logitech G Pro X Superlight 2 Black</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>840.00</t>
-        </is>
+      <c r="C123" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D123" t="n">
+        <v>400</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F123" t="n">
+        <v>840</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -6208,25 +5232,17 @@
           <t>Zowie Ergo Mouse (Unreleased)</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>620.00</t>
-        </is>
+      <c r="C124" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D124" t="n">
+        <v>400</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F124" t="n">
+        <v>620</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -6255,25 +5271,17 @@
           <t>Zowie Ergo Mouse (Unreleased)</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>640.00</t>
-        </is>
+      <c r="C125" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D125" t="n">
+        <v>400</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F125" t="n">
+        <v>640</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -6302,25 +5310,17 @@
           <t>Logitech G Pro X Superlight 2 Black</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>840</t>
-        </is>
+      <c r="C126" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D126" t="n">
+        <v>400</v>
+      </c>
+      <c r="E126" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F126" t="n">
+        <v>840</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -6349,25 +5349,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+      <c r="C127" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1000</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -6396,25 +5388,17 @@
           <t>Razer Viper V3 Pro Black</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>800.00</t>
-        </is>
+      <c r="C128" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D128" t="n">
+        <v>800</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>800</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -6443,25 +5427,17 @@
           <t>Pulsar eS FS-1</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="C129" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D129" t="n">
+        <v>400</v>
+      </c>
+      <c r="E129" t="n">
+        <v>2</v>
+      </c>
+      <c r="F129" t="n">
+        <v>800</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -6490,25 +5466,17 @@
           <t>Pulsar eS FS-1</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>1400.00</t>
-        </is>
+      <c r="C130" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D130" t="n">
+        <v>400</v>
+      </c>
+      <c r="E130" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1400</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -6537,25 +5505,17 @@
           <t>Lamzu Inca Black</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>0.825</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>1320.00</t>
-        </is>
+      <c r="C131" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1320</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -6584,25 +5544,17 @@
           <t>Razer Viper V3 Pro Green</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>780.00</t>
-        </is>
+      <c r="C132" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D132" t="n">
+        <v>400</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F132" t="n">
+        <v>780</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -6631,25 +5583,17 @@
           <t>Razer DeathAdder V4 Pro Black</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>740.00</t>
-        </is>
+      <c r="C133" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D133" t="n">
+        <v>400</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F133" t="n">
+        <v>740</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -6678,25 +5622,17 @@
           <t>ZOWIE EC2-DW Glossy</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>992.00</t>
-        </is>
+      <c r="C134" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D134" t="n">
+        <v>800</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F134" t="n">
+        <v>992</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -6725,25 +5661,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>960.00</t>
-        </is>
+      <c r="C135" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D135" t="n">
+        <v>800</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F135" t="n">
+        <v>960</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -6772,25 +5700,17 @@
           <t>Logitech G Pro X Superlight 2 White</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>1000.00</t>
-        </is>
+      <c r="C136" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D136" t="n">
+        <v>800</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1000</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -6819,25 +5739,17 @@
           <t>ZOWIE EC2-DW Black</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>800.00</t>
-        </is>
+      <c r="C137" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D137" t="n">
+        <v>400</v>
+      </c>
+      <c r="E137" t="n">
+        <v>2</v>
+      </c>
+      <c r="F137" t="n">
+        <v>800</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -6866,25 +5778,17 @@
           <t>Razer DeathAdder V4 Pro White</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>600.00</t>
-        </is>
+      <c r="C138" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D138" t="n">
+        <v>400</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F138" t="n">
+        <v>600</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -6913,25 +5817,17 @@
           <t>ZOWIE EC2-DW Black</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>760.00</t>
-        </is>
+      <c r="C139" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D139" t="n">
+        <v>800</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F139" t="n">
+        <v>760</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -6960,25 +5856,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>880.00</t>
-        </is>
+      <c r="C140" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D140" t="n">
+        <v>800</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F140" t="n">
+        <v>880</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -7007,25 +5895,17 @@
           <t>Logitech G Pro X Superlight 2 Magenta</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
+      <c r="C141" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D141" t="n">
+        <v>800</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1192</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -7054,25 +5934,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
+      <c r="C142" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D142" t="n">
+        <v>400</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F142" t="n">
+        <v>680</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -7101,25 +5973,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>800.00</t>
-        </is>
+      <c r="C143" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D143" t="n">
+        <v>800</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" t="n">
+        <v>800</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -7148,25 +6012,17 @@
           <t>Logitech G Pro X Superlight Black</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>920.00</t>
-        </is>
+      <c r="C144" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D144" t="n">
+        <v>800</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F144" t="n">
+        <v>920</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -7195,25 +6051,17 @@
           <t>Logitech G Pro X Superlight 2 White</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>804</t>
-        </is>
+      <c r="C145" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D145" t="n">
+        <v>400</v>
+      </c>
+      <c r="E145" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F145" t="n">
+        <v>804</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -7242,25 +6090,17 @@
           <t>ZOWIE S2-DW Black</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>720.00</t>
-        </is>
+      <c r="C146" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D146" t="n">
+        <v>800</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F146" t="n">
+        <v>720</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -7289,25 +6129,17 @@
           <t>Logitech G Pro X Superlight 2 Black</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>840.00</t>
-        </is>
+      <c r="C147" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D147" t="n">
+        <v>800</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F147" t="n">
+        <v>840</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -7336,25 +6168,17 @@
           <t>Razer Viper V3 Pro Faker Edition</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>760.00</t>
-        </is>
+      <c r="C148" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D148" t="n">
+        <v>400</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F148" t="n">
+        <v>760</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -7383,25 +6207,17 @@
           <t>Razer DeathAdder V4 Pro Black</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>840.00</t>
-        </is>
+      <c r="C149" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D149" t="n">
+        <v>800</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F149" t="n">
+        <v>840</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -7430,25 +6246,17 @@
           <t>Logitech G Pro X Superlight Black</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>840.00</t>
-        </is>
+      <c r="C150" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D150" t="n">
+        <v>400</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>840</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -7477,25 +6285,17 @@
           <t>Logitech G Pro X Superlight 2 Black</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>600.00</t>
-        </is>
+      <c r="C151" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D151" t="n">
+        <v>400</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F151" t="n">
+        <v>600</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -7524,25 +6324,17 @@
           <t>Logitech G Pro X Superlight 2 Magenta</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>920.00</t>
-        </is>
+      <c r="C152" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D152" t="n">
+        <v>400</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F152" t="n">
+        <v>920</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -7571,25 +6363,17 @@
           <t>Logitech G Pro X Superlight 2 Black</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>720.00</t>
-        </is>
+      <c r="C153" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D153" t="n">
+        <v>800</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F153" t="n">
+        <v>720</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -7618,25 +6402,17 @@
           <t>Razer Viper V4 Pro Black</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
+      <c r="C154" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D154" t="n">
+        <v>800</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F154" t="n">
+        <v>720</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -7665,25 +6441,17 @@
           <t>Razer Viper V3 Pro Dragon Lore Edition</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>560.00</t>
-        </is>
+      <c r="C155" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D155" t="n">
+        <v>800</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F155" t="n">
+        <v>560</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -7712,25 +6480,17 @@
           <t>Razer Viper V3 Pro White</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
+      <c r="C156" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D156" t="n">
+        <v>400</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F156" t="n">
+        <v>960</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -7759,25 +6519,17 @@
           <t>ZOWIE FK2-DW Black</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>720.00</t>
-        </is>
+      <c r="C157" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D157" t="n">
+        <v>800</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F157" t="n">
+        <v>720</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -7806,25 +6558,17 @@
           <t>Finalmouse Ultralight X Medium</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>760.00</t>
-        </is>
+      <c r="C158" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D158" t="n">
+        <v>800</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F158" t="n">
+        <v>760</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -7853,25 +6597,17 @@
           <t>Logitech G Pro X Superlight Black</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
+      <c r="C159" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D159" t="n">
+        <v>450</v>
+      </c>
+      <c r="E159" t="n">
+        <v>2</v>
+      </c>
+      <c r="F159" t="n">
+        <v>900</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -7900,25 +6636,17 @@
           <t>VAXEE XE V2 Lake Green</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>880.00</t>
-        </is>
+      <c r="C160" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D160" t="n">
+        <v>400</v>
+      </c>
+      <c r="E160" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F160" t="n">
+        <v>880</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -7947,25 +6675,17 @@
           <t>Logitech G Pro X Superlight 2 White</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>680.00</t>
-        </is>
+      <c r="C161" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D161" t="n">
+        <v>400</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F161" t="n">
+        <v>680</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -7994,25 +6714,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>1016.00</t>
-        </is>
+      <c r="C162" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D162" t="n">
+        <v>800</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1016</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -8041,25 +6753,17 @@
           <t>Lamzu Maya X Purple Shadow</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+      <c r="C163" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D163" t="n">
+        <v>400</v>
+      </c>
+      <c r="E163" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1000</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -8088,25 +6792,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>576</t>
-        </is>
+      <c r="C164" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D164" t="n">
+        <v>800</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F164" t="n">
+        <v>576</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -8135,25 +6831,17 @@
           <t>Pulsar ZywOo The Chosen Mouse Gen.2</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>3200</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>0.225</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>720.00</t>
-        </is>
+      <c r="C165" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D165" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="F165" t="n">
+        <v>720</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -8182,25 +6870,17 @@
           <t>Logitech G Pro X2 SUPERSTRIKE</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>840.00</t>
-        </is>
+      <c r="C166" t="n">
+        <v>500</v>
+      </c>
+      <c r="D166" t="n">
+        <v>800</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F166" t="n">
+        <v>840</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -8229,25 +6909,17 @@
           <t>Pulsar ZywOo The Chosen Mouse White</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>1040.00</t>
-        </is>
+      <c r="C167" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D167" t="n">
+        <v>800</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1040</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
